--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,6 +1536,103 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128774907</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ekebytorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>696264</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6617966</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sara Janbrink</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Janbrink</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,613 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129171396</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105719</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>696204</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6617846</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129171397</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105719</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>696153</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6617932</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129171387</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>696186</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6617866</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129171398</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105719</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>696151</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6617915</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129171372</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>696222</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6617653</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129174974</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105719</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>696136</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6617944</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,61 +1829,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171387</v>
+        <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>105722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696186</v>
+        <v>696151</v>
       </c>
       <c r="R12" t="n">
-        <v>6617866</v>
+        <v>6617915</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1908,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1943,45 +1926,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171398</v>
+        <v>129171372</v>
       </c>
       <c r="B13" t="n">
-        <v>105719</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696151</v>
+        <v>696222</v>
       </c>
       <c r="R13" t="n">
-        <v>6617915</v>
+        <v>6617653</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,53 +2031,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171372</v>
+        <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>105722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696222</v>
+        <v>696136</v>
       </c>
       <c r="R14" t="n">
-        <v>6617653</v>
+        <v>6617944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,57 +2116,73 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129174974</v>
+        <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>105719</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696136</v>
+        <v>696186</v>
       </c>
       <c r="R15" t="n">
-        <v>6617944</v>
+        <v>6617866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,24 +2217,30 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I 80-årig tallskog. Nära den gamla vägen där det växer små granar som skuggar. I övrigt ser skogen för torr och ljusöppen ut för knärot.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>129171372</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>129171372</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>129171396</v>
       </c>
       <c r="B10" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129171397</v>
       </c>
       <c r="B11" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>129171398</v>
       </c>
       <c r="B12" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>129171372</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>129174974</v>
       </c>
       <c r="B14" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>129171387</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696242.0486515763</v>
+        <v>696242</v>
       </c>
       <c r="R2" t="n">
-        <v>6617746.718179099</v>
+        <v>6617747</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1990-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2230,6 +2230,976 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131728915</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58270</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696274</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6617865</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131728910</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>696180</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6617685</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131728914</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>696314</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6617832</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131728918</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106160</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696206</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6617849</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131728909</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>696187</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6617677</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131728911</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696172</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6617710</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131728912</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93110</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>696197</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6617730</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131728916</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696274</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6617865</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131728920</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93110</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696119</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6617855</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131728921</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696145</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6617782</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>97904</v>
+        <v>97905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B20" t="n">
-        <v>93154</v>
+        <v>93116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R20" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B21" t="n">
-        <v>93116</v>
+        <v>93154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R21" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>97905</v>
+        <v>97906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131728915</v>
       </c>
       <c r="B16" t="n">
-        <v>58270</v>
+        <v>58271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>131728910</v>
       </c>
       <c r="B17" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131728914</v>
       </c>
       <c r="B18" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106160</v>
+        <v>106161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B20" t="n">
-        <v>93116</v>
+        <v>93155</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R20" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B21" t="n">
-        <v>93154</v>
+        <v>93117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R21" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2817,7 @@
         <v>131728912</v>
       </c>
       <c r="B22" t="n">
-        <v>93110</v>
+        <v>93111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>131728916</v>
       </c>
       <c r="B23" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>131728920</v>
       </c>
       <c r="B24" t="n">
-        <v>93110</v>
+        <v>93111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>131728921</v>
       </c>
       <c r="B25" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>97906</v>
+        <v>97909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131728915</v>
       </c>
       <c r="B16" t="n">
-        <v>58271</v>
+        <v>58274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>131728910</v>
       </c>
       <c r="B17" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131728914</v>
       </c>
       <c r="B18" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106161</v>
+        <v>106159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B20" t="n">
-        <v>93155</v>
+        <v>93120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R20" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B21" t="n">
-        <v>93117</v>
+        <v>93158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R21" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2817,7 @@
         <v>131728912</v>
       </c>
       <c r="B22" t="n">
-        <v>93111</v>
+        <v>93114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>131728916</v>
       </c>
       <c r="B23" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>131728920</v>
       </c>
       <c r="B24" t="n">
-        <v>93111</v>
+        <v>93114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>131728921</v>
       </c>
       <c r="B25" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B20" t="n">
-        <v>93120</v>
+        <v>93158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R20" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B21" t="n">
-        <v>93158</v>
+        <v>93120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R21" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>97909</v>
+        <v>97915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131728915</v>
       </c>
       <c r="B16" t="n">
-        <v>58274</v>
+        <v>58276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>131728910</v>
       </c>
       <c r="B17" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131728914</v>
       </c>
       <c r="B18" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>131728909</v>
       </c>
       <c r="B20" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>131728911</v>
       </c>
       <c r="B21" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131728912</v>
       </c>
       <c r="B22" t="n">
-        <v>93114</v>
+        <v>93120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>131728916</v>
       </c>
       <c r="B23" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>131728920</v>
       </c>
       <c r="B24" t="n">
-        <v>93114</v>
+        <v>93120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>131728921</v>
       </c>
       <c r="B25" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>97915</v>
+        <v>97918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131728915</v>
       </c>
       <c r="B16" t="n">
-        <v>58276</v>
+        <v>58279</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>131728910</v>
       </c>
       <c r="B17" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131728914</v>
       </c>
       <c r="B18" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106166</v>
+        <v>106170</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B20" t="n">
-        <v>93164</v>
+        <v>93129</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R20" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B21" t="n">
-        <v>93126</v>
+        <v>93167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R21" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2817,7 @@
         <v>131728912</v>
       </c>
       <c r="B22" t="n">
-        <v>93120</v>
+        <v>93123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>131728916</v>
       </c>
       <c r="B23" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>131728920</v>
       </c>
       <c r="B24" t="n">
-        <v>93120</v>
+        <v>93123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>131728921</v>
       </c>
       <c r="B25" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>97918</v>
+        <v>97923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131728915</v>
       </c>
       <c r="B16" t="n">
-        <v>58279</v>
+        <v>58284</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>131728910</v>
       </c>
       <c r="B17" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131728914</v>
       </c>
       <c r="B18" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106170</v>
+        <v>106175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B20" t="n">
-        <v>93129</v>
+        <v>93172</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R20" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B21" t="n">
-        <v>93167</v>
+        <v>93134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R21" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2817,7 @@
         <v>131728912</v>
       </c>
       <c r="B22" t="n">
-        <v>93123</v>
+        <v>93128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>131728916</v>
       </c>
       <c r="B23" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>131728920</v>
       </c>
       <c r="B24" t="n">
-        <v>93123</v>
+        <v>93128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>131728921</v>
       </c>
       <c r="B25" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69618973</v>
       </c>
       <c r="B2" t="n">
-        <v>97923</v>
+        <v>97925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>131728915</v>
       </c>
       <c r="B16" t="n">
-        <v>58284</v>
+        <v>58286</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>131728910</v>
       </c>
       <c r="B17" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131728914</v>
       </c>
       <c r="B18" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106175</v>
+        <v>106178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B20" t="n">
-        <v>93172</v>
+        <v>93136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R20" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B21" t="n">
-        <v>93134</v>
+        <v>93174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R21" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2817,7 @@
         <v>131728912</v>
       </c>
       <c r="B22" t="n">
-        <v>93128</v>
+        <v>93130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>131728916</v>
       </c>
       <c r="B23" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>131728920</v>
       </c>
       <c r="B24" t="n">
-        <v>93128</v>
+        <v>93130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>131728921</v>
       </c>
       <c r="B25" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -2620,32 +2620,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728911</v>
+        <v>131728909</v>
       </c>
       <c r="B20" t="n">
-        <v>93136</v>
+        <v>93174</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696172</v>
+        <v>696187</v>
       </c>
       <c r="R20" t="n">
-        <v>6617710</v>
+        <v>6617677</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728909</v>
+        <v>131728911</v>
       </c>
       <c r="B21" t="n">
-        <v>93174</v>
+        <v>93136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696187</v>
+        <v>696172</v>
       </c>
       <c r="R21" t="n">
-        <v>6617677</v>
+        <v>6617710</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -2235,7 +2235,7 @@
         <v>131728915</v>
       </c>
       <c r="B16" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>131728910</v>
       </c>
       <c r="B17" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>131728914</v>
       </c>
       <c r="B18" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>131728918</v>
       </c>
       <c r="B19" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>131728909</v>
       </c>
       <c r="B20" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>131728911</v>
       </c>
       <c r="B21" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>131728912</v>
       </c>
       <c r="B22" t="n">
-        <v>93171</v>
+        <v>93174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>131728916</v>
       </c>
       <c r="B23" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>131728920</v>
       </c>
       <c r="B24" t="n">
-        <v>93171</v>
+        <v>93174</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>131728921</v>
       </c>
       <c r="B25" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69618973</v>
+        <v>113189860</v>
       </c>
       <c r="B2" t="n">
-        <v>97925</v>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mittför Hållvastbyavtaget, avtag mot militärförråd, Upl</t>
+          <t>Sandamossen, SW om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696242</v>
+        <v>696160</v>
       </c>
       <c r="R2" t="n">
-        <v>6617747</v>
+        <v>6617743</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1990-01-01</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter. Lokalen först funnen av Tore Andersson</t>
+          <t>Nära bommen, både N och S om grusväg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,59 +770,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bill Douhan</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Upplands Flora 2010</t>
+          <t>Svampar i Roslagen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113189917</v>
+        <v>113189923</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -872,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära mindre grusgrop.</t>
+          <t>I mindre grusgrop.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113189923</v>
+        <v>113189917</v>
       </c>
       <c r="B4" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -995,7 +997,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I mindre grusgrop.</t>
+          <t>Nära mindre grusgrop.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,66 +1029,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113189799</v>
+        <v>131728912</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandamossen, S om, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696148</v>
+        <v>696197</v>
       </c>
       <c r="R5" t="n">
-        <v>6617933</v>
+        <v>6617730</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,17 +1094,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Östra delen av sluttning, några meter från äldre basväg. Nära liten grusgrop.</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,81 +1108,63 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113189823</v>
+        <v>131728920</v>
       </c>
       <c r="B6" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandamossen, S om, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696109</v>
+        <v>696119</v>
       </c>
       <c r="R6" t="n">
-        <v>6617941</v>
+        <v>6617855</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,17 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Talrik på sandig mark, NW om äldre, mindre grusgrop.</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,34 +1205,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113189860</v>
+        <v>131728910</v>
       </c>
       <c r="B7" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,45 +1234,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandamossen, SW om, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696160</v>
+        <v>696180</v>
       </c>
       <c r="R7" t="n">
-        <v>6617743</v>
+        <v>6617685</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,17 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Nära bommen, både N och S om grusväg.</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,88 +1302,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121325930</v>
+        <v>131728911</v>
       </c>
       <c r="B8" t="n">
-        <v>57726</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SO Hållvastby grustag, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696225</v>
+        <v>696172</v>
       </c>
       <c r="R8" t="n">
-        <v>6617816</v>
+        <v>6617710</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,27 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Förmodligen fler - i meståg.</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,57 +1405,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128774907</v>
+        <v>131728914</v>
       </c>
       <c r="B9" t="n">
-        <v>8439</v>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ekebytorp, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696264</v>
+        <v>696314</v>
       </c>
       <c r="R9" t="n">
-        <v>6617966</v>
+        <v>6617832</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1588,12 +1482,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,60 +1502,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sara Janbrink</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sara Janbrink</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129171396</v>
+        <v>131728921</v>
       </c>
       <c r="B10" t="n">
-        <v>105822</v>
+        <v>93271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696204</v>
+        <v>696145</v>
       </c>
       <c r="R10" t="n">
-        <v>6617846</v>
+        <v>6617782</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,12 +1579,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,60 +1599,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129171397</v>
+        <v>131728909</v>
       </c>
       <c r="B11" t="n">
-        <v>105822</v>
+        <v>93309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696153</v>
+        <v>696187</v>
       </c>
       <c r="R11" t="n">
-        <v>6617932</v>
+        <v>6617677</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1782,12 +1676,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,22 +1696,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129171398</v>
+        <v>129171372</v>
       </c>
       <c r="B12" t="n">
-        <v>105822</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,34 +1719,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696151</v>
+        <v>696222</v>
       </c>
       <c r="R12" t="n">
-        <v>6617915</v>
+        <v>6617653</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,27 +1813,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129171372</v>
+        <v>121325930</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1939,25 +1841,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>SO Hållvastby grustag, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696222</v>
+        <v>696225</v>
       </c>
       <c r="R13" t="n">
-        <v>6617653</v>
+        <v>6617816</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,12 +1890,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Förmodligen fler - i meståg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,22 +1925,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129174974</v>
+        <v>131728915</v>
       </c>
       <c r="B14" t="n">
-        <v>105822</v>
+        <v>58349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,37 +1948,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696136</v>
+        <v>696274</v>
       </c>
       <c r="R14" t="n">
-        <v>6617944</v>
+        <v>6617865</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,12 +2002,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,76 +2022,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171387</v>
+        <v>131728916</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållvastby, Upl</t>
+          <t>Hålvastby Riala, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696186</v>
+        <v>696274</v>
       </c>
       <c r="R15" t="n">
-        <v>6617866</v>
+        <v>6617865</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,17 +2099,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I 80-årig tallskog. Nära den gamla vägen där det växer små granar som skuggar. I övrigt ser skogen för torr och ljusöppen ut för knärot.</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,29 +2113,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131728915</v>
+        <v>128774907</v>
       </c>
       <c r="B16" t="n">
-        <v>58322</v>
+        <v>8444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,34 +2142,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Ekebytorp, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696274</v>
+        <v>696264</v>
       </c>
       <c r="R16" t="n">
-        <v>6617865</v>
+        <v>6617966</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2297,12 +2196,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,57 +2216,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Sara Janbrink</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Sara Janbrink</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131728910</v>
+        <v>113189799</v>
       </c>
       <c r="B17" t="n">
-        <v>93180</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Sandamossen, S om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696180</v>
+        <v>696148</v>
       </c>
       <c r="R17" t="n">
-        <v>6617685</v>
+        <v>6617933</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2394,12 +2309,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Östra delen av sluttning, några meter från äldre basväg. Nära liten grusgrop.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2408,66 +2328,83 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131728914</v>
+        <v>129171387</v>
       </c>
       <c r="B18" t="n">
-        <v>93180</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696314</v>
+        <v>696186</v>
       </c>
       <c r="R18" t="n">
-        <v>6617832</v>
+        <v>6617866</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2491,12 +2428,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I 80-årig tallskog. Nära den gamla vägen där det växer små granar som skuggar. I övrigt ser skogen för torr och ljusöppen ut för knärot.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,66 +2447,83 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131728918</v>
+        <v>129171388</v>
       </c>
       <c r="B19" t="n">
-        <v>106222</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696206</v>
+        <v>696167</v>
       </c>
       <c r="R19" t="n">
-        <v>6617849</v>
+        <v>6617626</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,12 +2547,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>9 blomställningar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2602,66 +2566,83 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131728909</v>
+        <v>129171390</v>
       </c>
       <c r="B20" t="n">
-        <v>93218</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696187</v>
+        <v>696154</v>
       </c>
       <c r="R20" t="n">
-        <v>6617677</v>
+        <v>6617648</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,12 +2666,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,50 +2685,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131728911</v>
+        <v>131728878</v>
       </c>
       <c r="B21" t="n">
-        <v>93180</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696172</v>
+        <v>696164</v>
       </c>
       <c r="R21" t="n">
-        <v>6617710</v>
+        <v>6617631</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2788,6 +2775,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stora mängder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,45 +2806,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131728912</v>
+        <v>113189823</v>
       </c>
       <c r="B22" t="n">
-        <v>93174</v>
+        <v>106244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Sandamossen, S om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696197</v>
+        <v>696109</v>
       </c>
       <c r="R22" t="n">
-        <v>6617730</v>
+        <v>6617941</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2879,12 +2883,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Talrik på sandig mark, NW om äldre, mindre grusgrop.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2893,66 +2902,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131728916</v>
+        <v>129171396</v>
       </c>
       <c r="B23" t="n">
-        <v>58109</v>
+        <v>106243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696274</v>
+        <v>696204</v>
       </c>
       <c r="R23" t="n">
-        <v>6617865</v>
+        <v>6617846</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2976,12 +2986,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,60 +3006,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131728920</v>
+        <v>129171397</v>
       </c>
       <c r="B24" t="n">
-        <v>93174</v>
+        <v>106243</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696119</v>
+        <v>696153</v>
       </c>
       <c r="R24" t="n">
-        <v>6617855</v>
+        <v>6617932</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3073,12 +3083,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3093,22 +3103,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131728921</v>
+        <v>129171398</v>
       </c>
       <c r="B25" t="n">
-        <v>93180</v>
+        <v>106243</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,37 +3126,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hålvastby Riala, Upl</t>
+          <t>Hållvastby, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696145</v>
+        <v>696151</v>
       </c>
       <c r="R25" t="n">
-        <v>6617782</v>
+        <v>6617915</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3170,12 +3180,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3190,15 +3200,315 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129174974</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hållvastby, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696136</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6617944</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131728918</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hålvastby Riala, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696206</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6617849</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Johan Kjetselberg</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Niina Sallmén</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>69618973</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mittför Hållvastbyavtaget, avtag mot militärförråd, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>696242</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6617747</v>
+      </c>
+      <c r="S28" t="n">
+        <v>100</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter. Lokalen först funnen av Tore Andersson</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bill Douhan</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25732-2025 artfynd.xlsx
+++ b/artfynd/A 25732-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113189860</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113189923</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113189917</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728920</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728910</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728911</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728914</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728921</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728909</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171372</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121325930</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728915</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728916</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2225,6 +2300,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128774907</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113189799</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2463,6 +2548,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171387</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2582,6 +2672,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171388</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2701,6 +2796,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171390</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2803,6 +2903,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728878</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2918,6 +3023,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113189823</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171396</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3112,6 +3227,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171397</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171398</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3306,6 +3431,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174974</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3403,6 +3533,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728918</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3509,8 +3644,42 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69618973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>